--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-observation-vital-sign.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-vital-sign.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-vital-sign.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-vital-sign.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-vital-sign.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-vital-sign.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-vital-sign.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -792,7 +796,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1757,13 +1761,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1814,7 +1818,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1831,10 +1835,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1857,13 +1861,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1914,7 +1918,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1931,10 +1935,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1957,13 +1961,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2014,7 +2018,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2031,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2057,13 +2061,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2114,7 +2118,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2131,10 +2135,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2157,13 +2161,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2214,7 +2218,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2231,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2257,13 +2261,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2314,7 +2318,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2331,10 +2335,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2357,13 +2361,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2414,7 +2418,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2431,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2457,13 +2461,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2493,10 +2497,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2514,7 +2518,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2531,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2557,13 +2561,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2614,7 +2618,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2631,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2657,13 +2661,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2714,7 +2718,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2731,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2757,13 +2761,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2814,7 +2818,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2831,10 +2835,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2857,13 +2861,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2914,7 +2918,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -2931,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2957,13 +2961,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2993,10 +2997,10 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3014,7 +3018,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3031,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3057,13 +3061,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3114,7 +3118,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="165">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-observation-vital-sign.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-observation-vital-sign.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-observation-vital-sign.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-observation-vital-sign.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-observation-vital-sign.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-vital-sign.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-vital-sign.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-vital-sign.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-vital-sign.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-vital-sign.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-observation-vital-sign.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-observation-vital-sign.header.source</t>
+    <t>fr-lm-observation-vital-sign.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-vital-sign.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -783,11 +825,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ23"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.87890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.87890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.58984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="58.58984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -796,7 +838,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -817,7 +859,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.97265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1561,13 +1603,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1618,7 +1660,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1635,10 +1677,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1661,13 +1703,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1718,7 +1760,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1735,10 +1777,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1761,13 +1803,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1818,7 +1860,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1835,10 +1877,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1861,7 +1903,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -1961,13 +2003,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2018,7 +2060,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2035,10 +2077,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2049,7 +2091,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2061,13 +2103,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2118,13 +2160,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2135,10 +2177,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2149,7 +2191,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2161,13 +2203,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2218,13 +2260,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2235,10 +2277,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2249,7 +2291,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2261,13 +2303,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2318,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2335,10 +2377,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2346,7 +2388,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2361,13 +2403,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2418,10 +2460,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2435,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2461,7 +2503,7 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>132</v>
@@ -2518,7 +2560,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2535,10 +2577,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2546,7 +2588,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2561,7 +2603,7 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>137</v>
@@ -2618,10 +2660,10 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2635,10 +2677,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2661,13 +2703,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2718,7 +2760,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2735,10 +2777,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2746,7 +2788,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>79</v>
@@ -2761,13 +2803,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2818,10 +2860,10 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>79</v>
@@ -2835,10 +2877,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2861,13 +2903,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2897,10 +2939,10 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -2918,7 +2960,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -2935,10 +2977,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2946,10 +2988,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -2961,13 +3003,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2997,10 +3039,10 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3018,13 +3060,13 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
@@ -3035,10 +3077,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3061,13 +3103,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3118,7 +3160,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3130,6 +3172,406 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="166">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,6 +493,10 @@
   </si>
   <si>
     <t>fr-lm-observation-vital-sign.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Site de l'observation</t>
@@ -3203,13 +3207,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3277,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3306,10 +3310,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3360,7 +3364,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3377,10 +3381,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3406,10 +3410,10 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3439,10 +3443,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3460,7 +3464,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3477,10 +3481,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3503,13 +3507,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3560,7 +3564,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
